--- a/artfynd/A 11048-2026 artfynd.xlsx
+++ b/artfynd/A 11048-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,6 +1128,112 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132133120</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104559</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Säby västerskog, S, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>544986</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6456498</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vist</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11048-2026 artfynd.xlsx
+++ b/artfynd/A 11048-2026 artfynd.xlsx
@@ -1133,7 +1133,7 @@
         <v>132133120</v>
       </c>
       <c r="B6" t="n">
-        <v>104559</v>
+        <v>104562</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11048-2026 artfynd.xlsx
+++ b/artfynd/A 11048-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112567618</v>
+        <v>132133154</v>
       </c>
       <c r="B2" t="n">
-        <v>99160</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,47 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>1444</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dunderhult, Ög</t>
+          <t>Mumsmålen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545017</v>
+        <v>545289</v>
       </c>
       <c r="R2" t="n">
-        <v>6456542</v>
+        <v>6456700</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,50 +761,46 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Alfred Berencreutz, Emma Berencreutz, Tommy Carlström</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112567560</v>
+        <v>112567605</v>
       </c>
       <c r="B3" t="n">
-        <v>102466</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,7 +819,7 @@
         <v>545017</v>
       </c>
       <c r="R3" t="n">
-        <v>6456542</v>
+        <v>6456543</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -910,19 +888,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112567605</v>
+        <v>126053859</v>
       </c>
       <c r="B4" t="n">
-        <v>109056</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -944,17 +917,20 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dunderhult, Ög</t>
+          <t>Mumsmålen, SV, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545017</v>
+        <v>545071</v>
       </c>
       <c r="R4" t="n">
-        <v>6456542</v>
+        <v>6456530</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,28 +971,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Alfred Berencreutz, Emma Berencreutz, Tommy Carlström</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126053859</v>
+        <v>112567560</v>
       </c>
       <c r="B5" t="n">
-        <v>110452</v>
+        <v>104628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,16 +1006,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219711</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1052,20 +1024,17 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ngt, Ög</t>
+          <t>Dunderhult, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545070</v>
+        <v>545017</v>
       </c>
       <c r="R5" t="n">
-        <v>6456530</v>
+        <v>6456543</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,12 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,24 +1085,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Ingela Carlström, Alfred Berencreutz, Emma Berencreutz, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1133,7 +1106,7 @@
         <v>132133120</v>
       </c>
       <c r="B6" t="n">
-        <v>104632</v>
+        <v>104707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,6 +1207,123 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112567618</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dunderhult, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>545017</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6456543</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vist</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ingela Carlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ingela Carlström, Alfred Berencreutz, Emma Berencreutz, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11048-2026 artfynd.xlsx
+++ b/artfynd/A 11048-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132133154</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112567605</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126053859</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112567560</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132133120</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,8 +1353,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112567618</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>